--- a/forms/trg/Formulir_TRG_srcrg.xlsx
+++ b/forms/trg/Formulir_TRG_srcrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B30)</f>
+        <f>COUNTA(Anggota!B5:B31)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F30)</f>
+        <f>COUNTA(Anggota!F5:F31)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,37 +913,33 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Jamaluddin Jompa, M.Sc.</t>
+          <t>Prof. Dr. Ir. Chair Rani. M,Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Marine Ecology</t>
+          <t>Coral Reef Ecology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-9740-333X</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>258630</t>
+          <t>6038272</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>6603032552</t>
+          <t>55977731600</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,18 +954,18 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Abdul Haris, M.Si.</t>
+          <t>Prof. Dr. Ir. Jamaluddin Jompa, M.Sc.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Marine Biology</t>
+          <t>Marine Ecology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -978,17 +974,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7535-4514</t>
+          <t>0000-0001-9740-333X</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6023106</t>
+          <t>258630</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>56581763400</t>
+          <t>6603032552</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,18 +999,18 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Rohani AR, M.Si.</t>
+          <t>Prof. Dr. Ir. Abdul Haris, M.Si.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Seagrass Ecology</t>
+          <t>Marine Biology</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1023,17 +1019,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9276-7492</t>
+          <t>0000-0001-7535-4514</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>5973877</t>
+          <t>6023106</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57207452067</t>
+          <t>56581763400</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,18 +1044,18 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Budimawan, DEA</t>
+          <t>Prof. Dr. Ir. Rohani AR, M.Si.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Fisheries Biology</t>
+          <t>Seagrass Ecology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1068,17 +1064,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0566-2305</t>
+          <t>0000-0001-9276-7492</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6005344</t>
+          <t>5973877</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>7409768808</t>
+          <t>57207452067</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,33 +1089,37 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Andi Iqbal Burhanuddin, S.T., M.Fish.Sc., Ph.D.</t>
+          <t>Prof. Dr. Ir. Budimawan, DEA</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Marine Ichtiology</t>
+          <t>Fisheries Biology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0566-2305</t>
+        </is>
+      </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>5974629</t>
+          <t>6005344</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57215376841</t>
+          <t>7409768808</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1134,37 +1134,33 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Rahmadi Tambaru, M.Si.</t>
+          <t>Prof. Andi Iqbal Burhanuddin, S.T., M.Fish.Sc., Ph.D.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Marine Plankton</t>
+          <t>Marine Ichtiology</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-9403-0697</t>
-        </is>
-      </c>
+      <c r="J10" s="12" t="n"/>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6005441</t>
+          <t>5974629</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57192890689</t>
+          <t>57215376841</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1179,33 +1175,37 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Nadiarti, M.Sc.</t>
+          <t>Prof. Dr. Ir. Rahmadi Tambaru, M.Si.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Marine Biodiversity</t>
+          <t>Marine Plankton</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-9403-0697</t>
+        </is>
+      </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>6007052</t>
+          <t>6005441</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57221441941</t>
+          <t>57192890689</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1220,37 +1220,33 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Wasir Samad, S.Si. M.Si.</t>
+          <t>Prof. Dr. Ir. Nadiarti, M.Sc.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Phisical Oseanografi</t>
+          <t>Marine Biodiversity</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2135-3177</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>6669349</t>
+          <t>6007052</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>57202443196</t>
+          <t>57221441941</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1265,18 +1261,18 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Widyastuti, S.Kel.</t>
+          <t>Dr. Wasir Samad, S.Si. M.Si.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Marine Genetic</t>
+          <t>Phisical Oseanografi</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1285,17 +1281,17 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0763-6581</t>
+          <t>0000-0002-2135-3177</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>6782473</t>
+          <t>6669349</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>57200720560</t>
+          <t>57202443196</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1310,31 +1306,39 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Andi Annisar Dzati Iffah, S.Kel., M.Si</t>
+          <t>Dr. Widyastuti, S.Kel.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Shark and Ray Biology</t>
+          <t>Marine Genetic</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0763-6581</t>
+        </is>
+      </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>6941539</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="n"/>
+          <t>6782473</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>57200720560</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1347,12 +1351,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Michael Grant</t>
+          <t>Andi Annisar Dzati Iffah, S.Kel., M.Si</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1366,7 +1370,11 @@
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>6941539</t>
+        </is>
+      </c>
       <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
@@ -1380,18 +1388,18 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Funty Septiyawati Polapa</t>
+          <t>Michael Grant</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Shark and Ray Biology</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1399,11 +1407,7 @@
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>6718253</t>
-        </is>
-      </c>
+      <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
@@ -1417,12 +1421,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Rara Adesuara Sari</t>
+          <t>Funty Septiyawati Polapa</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1436,7 +1440,11 @@
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>6718253</t>
+        </is>
+      </c>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="11" t="inlineStr">
         <is>
@@ -1450,12 +1458,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fahmi Djunaid</t>
+          <t>Rara Adesuara Sari</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1481,10 +1489,26 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Muhammad Fahmi Djunaid</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Sharks and rays are important components of marine ecosystems and play a key role in maintaining ocean health. However, many shark and ray species are increasingly threatened by overfishing, bycatch, habitat loss, and illegal trade. Their slow growth and low reproductive rates make them especially vulnerable to population decline.</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1492,7 +1516,11 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1681,15 +1709,32 @@
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
